--- a/diseases/d236/2020-2025.xlsx
+++ b/diseases/d236/2020-2025.xlsx
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN38" t="b">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN50" t="b">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -14085,7 +14085,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15657,7 +15657,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16443,7 +16443,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17229,7 +17229,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -18015,7 +18015,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18801,7 +18801,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19587,7 +19587,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20373,7 +20373,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -21562,7 +21562,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22348,7 +22348,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23920,7 +23920,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24706,7 +24706,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25492,7 +25492,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26278,7 +26278,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -27064,7 +27064,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27850,7 +27850,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28636,7 +28636,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29422,7 +29422,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -30208,7 +30208,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -31397,7 +31397,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -32183,7 +32183,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -32969,7 +32969,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -33755,7 +33755,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -34541,7 +34541,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -35327,7 +35327,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -36113,7 +36113,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -36899,7 +36899,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -37685,7 +37685,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -38471,7 +38471,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -39257,7 +39257,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -40043,7 +40043,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -41232,7 +41232,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -42018,7 +42018,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -42804,7 +42804,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -44376,7 +44376,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -45162,7 +45162,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -45948,7 +45948,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -46734,7 +46734,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -47520,7 +47520,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -48306,7 +48306,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -49092,7 +49092,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -49878,7 +49878,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -51067,7 +51067,7 @@
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN257" t="b">
@@ -51853,7 +51853,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -52639,7 +52639,7 @@
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN265" t="b">
@@ -53425,7 +53425,7 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -54211,7 +54211,7 @@
       </c>
       <c r="AM273" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN273" t="b">
@@ -54997,7 +54997,7 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN277" t="b">
@@ -55783,7 +55783,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -56569,7 +56569,7 @@
       </c>
       <c r="AM285" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN285" t="b">
@@ -57355,7 +57355,7 @@
       </c>
       <c r="AM289" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN289" t="b">
@@ -58141,7 +58141,7 @@
       </c>
       <c r="AM293" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN293" t="b">
@@ -58927,7 +58927,7 @@
       </c>
       <c r="AM297" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN297" t="b">
@@ -59713,7 +59713,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN301" t="b">

--- a/diseases/d236/2020-2025.xlsx
+++ b/diseases/d236/2020-2025.xlsx
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN38" t="b">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN50" t="b">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -14085,7 +14085,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15657,7 +15657,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16443,7 +16443,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17229,7 +17229,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -18015,7 +18015,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18801,7 +18801,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19587,7 +19587,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20373,7 +20373,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -21562,7 +21562,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22348,7 +22348,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23920,7 +23920,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24706,7 +24706,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25492,7 +25492,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26278,7 +26278,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -27064,7 +27064,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27850,7 +27850,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28636,7 +28636,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29422,7 +29422,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -30208,7 +30208,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -31397,7 +31397,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -32183,7 +32183,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -32969,7 +32969,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -33755,7 +33755,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -34541,7 +34541,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -35327,7 +35327,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -36113,7 +36113,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -36899,7 +36899,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -37685,7 +37685,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -38471,7 +38471,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -39257,7 +39257,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -40043,7 +40043,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -41232,7 +41232,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -42018,7 +42018,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -42804,7 +42804,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -44376,7 +44376,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -45162,7 +45162,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -45948,7 +45948,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -46734,7 +46734,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -47520,7 +47520,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -48306,7 +48306,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -49092,7 +49092,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -49878,7 +49878,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -51067,7 +51067,7 @@
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN257" t="b">
@@ -51853,7 +51853,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -52639,7 +52639,7 @@
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN265" t="b">
@@ -53425,7 +53425,7 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -54211,7 +54211,7 @@
       </c>
       <c r="AM273" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN273" t="b">
@@ -54997,7 +54997,7 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN277" t="b">
@@ -55783,7 +55783,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -56569,7 +56569,7 @@
       </c>
       <c r="AM285" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN285" t="b">
@@ -57355,7 +57355,7 @@
       </c>
       <c r="AM289" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN289" t="b">
@@ -58141,7 +58141,7 @@
       </c>
       <c r="AM293" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN293" t="b">
@@ -58927,7 +58927,7 @@
       </c>
       <c r="AM297" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN297" t="b">
@@ -59713,7 +59713,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN301" t="b">

--- a/diseases/d236/2020-2025.xlsx
+++ b/diseases/d236/2020-2025.xlsx
@@ -52781,13 +52781,13 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="O266" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="R266" t="n">
-        <v>3.162349683994936</v>
+        <v>3.15296585703946</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
@@ -52940,10 +52940,10 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="O267" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="U267" t="inlineStr">
         <is>
@@ -60359,7 +60359,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>36161</v>
+        <v>36160</v>
       </c>
     </row>
     <row r="16">
